--- a/Result/profitability/6642.xlsx
+++ b/Result/profitability/6642.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM38"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5256,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>180</v>
+      </c>
+      <c r="D39" t="n">
+        <v>83</v>
+      </c>
+      <c r="E39" t="n">
+        <v>97</v>
+      </c>
+      <c r="F39" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>56</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>31.02%</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>59</v>
+      </c>
+      <c r="K39" t="n">
+        <v>57</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.8162499999999999</v>
+      </c>
+      <c r="N39" t="n">
+        <v>47.24875</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.081081081081081</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>5.189999999999998</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.1068121012554022</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.380000000000003</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.159051724137931</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
